--- a/artfynd/A 72189-2021 artfynd.xlsx
+++ b/artfynd/A 72189-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9294,6 +9294,132 @@
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>101657543</v>
+      </c>
+      <c r="B77" t="n">
+        <v>90506</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Godkänd. Belägg granskat av validerare.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6008693</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Kritporing</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Resinoporia crassa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Audet</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Juvan, Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>432648</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6912125</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2022-05-23</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2022-05-23</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre fruktkropp vid basen av kolad låga. Området är avverkningsanmält</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>101657543</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 72189-2021 artfynd.xlsx
+++ b/artfynd/A 72189-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
